--- a/artfynd/A 26-2025 artfynd.xlsx
+++ b/artfynd/A 26-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>122047761</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>122311014</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 26-2025 artfynd.xlsx
+++ b/artfynd/A 26-2025 artfynd.xlsx
@@ -813,11 +813,6 @@
       <c r="E3" t="n">
         <v>100049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -914,11 +909,6 @@
       </c>
       <c r="E4" t="n">
         <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 26-2025 artfynd.xlsx
+++ b/artfynd/A 26-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>122311014</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,6 +909,11 @@
       </c>
       <c r="E4" t="n">
         <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 26-2025 artfynd.xlsx
+++ b/artfynd/A 26-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>122311014</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
